--- a/Controle_Operacional_Final.xlsx
+++ b/Controle_Operacional_Final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ARQUIVOS MERCEDES\Planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E1DC01-7744-482A-82A5-6AC71DAAFF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C782544C-EE9C-43F6-A5BA-25B834C234BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21480" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="339">
   <si>
     <t>📊  DASHBOARD — CONTROLE DE QUALIDADE OPERACIONAL</t>
   </si>
@@ -851,6 +851,213 @@
   </si>
   <si>
     <t xml:space="preserve">T006 040 09 </t>
+  </si>
+  <si>
+    <t>827858/001</t>
+  </si>
+  <si>
+    <t>B001 149 04</t>
+  </si>
+  <si>
+    <t>B001 146 04</t>
+  </si>
+  <si>
+    <t>760.033/001</t>
+  </si>
+  <si>
+    <t>B002 107 03</t>
+  </si>
+  <si>
+    <t>B002 107 02</t>
+  </si>
+  <si>
+    <t>628.695/001</t>
+  </si>
+  <si>
+    <t>B003 009 00</t>
+  </si>
+  <si>
+    <t>F044571</t>
+  </si>
+  <si>
+    <t>B003 008 00</t>
+  </si>
+  <si>
+    <t>635.150/001</t>
+  </si>
+  <si>
+    <t>B003 005 11</t>
+  </si>
+  <si>
+    <t>F044592</t>
+  </si>
+  <si>
+    <t>B003 002 11</t>
+  </si>
+  <si>
+    <t>647.377/001</t>
+  </si>
+  <si>
+    <t>B002 101 06</t>
+  </si>
+  <si>
+    <t>B003 101 06</t>
+  </si>
+  <si>
+    <t>647.378/001</t>
+  </si>
+  <si>
+    <t>B002 101 07</t>
+  </si>
+  <si>
+    <t>B003 101 07</t>
+  </si>
+  <si>
+    <t>661580/006</t>
+  </si>
+  <si>
+    <t>T001 022 05</t>
+  </si>
+  <si>
+    <t>T001 022 06</t>
+  </si>
+  <si>
+    <t>682.796/003</t>
+  </si>
+  <si>
+    <t>B002 117 01</t>
+  </si>
+  <si>
+    <t>B002 117 07</t>
+  </si>
+  <si>
+    <t>942.668/001</t>
+  </si>
+  <si>
+    <t>T005 053 01</t>
+  </si>
+  <si>
+    <t>T006 053 01</t>
+  </si>
+  <si>
+    <t>589.312/001</t>
+  </si>
+  <si>
+    <t>T008 029 02</t>
+  </si>
+  <si>
+    <t>F044582</t>
+  </si>
+  <si>
+    <t>T007 030 01</t>
+  </si>
+  <si>
+    <t>601165/001</t>
+  </si>
+  <si>
+    <t>T007 077 07</t>
+  </si>
+  <si>
+    <t>T007 077 01</t>
+  </si>
+  <si>
+    <t>703.985/005</t>
+  </si>
+  <si>
+    <t>T008 006 07</t>
+  </si>
+  <si>
+    <t>T008 007 05</t>
+  </si>
+  <si>
+    <t>733.765/004</t>
+  </si>
+  <si>
+    <t>T009 015 06</t>
+  </si>
+  <si>
+    <t>T008 015 06</t>
+  </si>
+  <si>
+    <t>630.367/011</t>
+  </si>
+  <si>
+    <t>T013 030 06</t>
+  </si>
+  <si>
+    <t>T011 030 06</t>
+  </si>
+  <si>
+    <t>748.904/001</t>
+  </si>
+  <si>
+    <t>T011 038 00</t>
+  </si>
+  <si>
+    <t>T012 038 00</t>
+  </si>
+  <si>
+    <t>740.829/005</t>
+  </si>
+  <si>
+    <t>T012 009 04</t>
+  </si>
+  <si>
+    <t>T012 001 004</t>
+  </si>
+  <si>
+    <t>620.096/007</t>
+  </si>
+  <si>
+    <t>T014 020 03</t>
+  </si>
+  <si>
+    <t>T014 020 04</t>
+  </si>
+  <si>
+    <t>973635/001</t>
+  </si>
+  <si>
+    <t>T015 023 04</t>
+  </si>
+  <si>
+    <t>T015 023 01</t>
+  </si>
+  <si>
+    <t>746.745/001</t>
+  </si>
+  <si>
+    <t>T015 029 01</t>
+  </si>
+  <si>
+    <t>T015 029 00</t>
+  </si>
+  <si>
+    <t>626.681/001</t>
+  </si>
+  <si>
+    <t>T013 69 05</t>
+  </si>
+  <si>
+    <t>T014 069 05</t>
+  </si>
+  <si>
+    <t>752.524/001</t>
+  </si>
+  <si>
+    <t>T013 053 05</t>
+  </si>
+  <si>
+    <t>T016 053 05</t>
+  </si>
+  <si>
+    <t>558.446/001</t>
+  </si>
+  <si>
+    <t>T019 014 08</t>
+  </si>
+  <si>
+    <t>T019 014 05</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1914,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1719,19 +1926,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>2</c:v>
-                </c:pt>
                 <c:pt idx="9">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2335,7 +2542,7 @@
       <c r="L6" s="53"/>
       <c r="M6" s="58">
         <f ca="1">SUMPRODUCT((YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))+SUMPRODUCT((YEAR(CONFERENTES!A3:A102)=YEAR(TODAY()))*(CONFERENTES!A3:A102&lt;&gt;""))</f>
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="N6" s="53"/>
       <c r="O6" s="53"/>
@@ -2407,7 +2614,7 @@
       <c r="N31" s="36"/>
       <c r="O31" s="42">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L31)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="12:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2459,7 +2666,7 @@
       <c r="N35" s="36"/>
       <c r="O35" s="42">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L35)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="12:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2485,7 +2692,7 @@
       <c r="N37" s="36"/>
       <c r="O37" s="41">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L37)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="12:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2498,7 +2705,7 @@
       <c r="N38" s="36"/>
       <c r="O38" s="33">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L38)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="12:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2511,7 +2718,7 @@
       <c r="N39" s="39"/>
       <c r="O39" s="40">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L39)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="12:15" x14ac:dyDescent="0.25">
@@ -2524,7 +2731,7 @@
       <c r="N40" s="36"/>
       <c r="O40" s="35">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L40)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="12:15" x14ac:dyDescent="0.25">
@@ -2571,7 +2778,7 @@
       <c r="N44" s="36"/>
       <c r="O44" s="35">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L44)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="12:15" x14ac:dyDescent="0.25">
@@ -2610,7 +2817,7 @@
       <c r="N47" s="36"/>
       <c r="O47" s="35">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L47)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="12:15" x14ac:dyDescent="0.25">
@@ -2662,7 +2869,7 @@
       <c r="N51" s="36"/>
       <c r="O51" s="35">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L51)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="12:15" x14ac:dyDescent="0.25">
@@ -2721,7 +2928,7 @@
       <c r="N56" s="36"/>
       <c r="O56" s="35">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,L56)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3764,180 +3971,444 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="3"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="A51" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
+      <c r="A52" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="3"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="A53" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
+      <c r="A54" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="A55" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6"/>
-      <c r="B56" s="7"/>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
+      <c r="A56" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="3"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="A57" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6"/>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
+      <c r="A58" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="A59" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="6"/>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
+      <c r="A60" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="3"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="A61" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="6"/>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
+      <c r="A62" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="A63" s="3">
+        <v>46168</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="6"/>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
+      <c r="A64" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="A65" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="6"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
+      <c r="A66" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="A67" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="6"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
+      <c r="A68" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="A69" s="3">
+        <v>46200</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="6"/>
-      <c r="B70" s="7"/>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
+      <c r="A70" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="A71" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="6"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
+      <c r="A72" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
@@ -5216,11 +5687,11 @@
       </c>
       <c r="F3" s="11">
         <f ca="1">SUMPRODUCT((MONTH('GUARDA MAT. ERRADO'!A3:A102)=5)*(YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))</f>
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G3" s="11">
         <f ca="1">SUMPRODUCT((MONTH('GUARDA MAT. ERRADO'!A3:A102)=6)*(YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H3" s="11">
         <f ca="1">SUMPRODUCT((MONTH('GUARDA MAT. ERRADO'!A3:A102)=7)*(YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))</f>
@@ -5322,11 +5793,11 @@
       </c>
       <c r="F5" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G5" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H5" s="14">
         <f t="shared" ca="1" si="0"/>
@@ -5383,7 +5854,7 @@
       </c>
       <c r="B9" s="26">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="25" t="s">
         <v>104</v>
@@ -5447,7 +5918,7 @@
       </c>
       <c r="B13" s="26">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A13)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" s="27" t="s">
         <v>108</v>
@@ -5479,7 +5950,7 @@
       </c>
       <c r="B15" s="26">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A15)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D15" s="28" t="s">
         <v>25</v>
@@ -5492,7 +5963,7 @@
       </c>
       <c r="B16" s="26">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A16)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="27" t="s">
         <v>83</v>
@@ -5508,7 +5979,7 @@
       </c>
       <c r="B17" s="26">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A17)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>110</v>
@@ -5524,7 +5995,7 @@
       </c>
       <c r="B18" s="32">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A18)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="27" t="s">
         <v>111</v>
@@ -5582,7 +6053,7 @@
       </c>
       <c r="B22" s="32">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A22)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
@@ -5615,7 +6086,7 @@
       </c>
       <c r="B25" s="32">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A25)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
@@ -5648,7 +6119,7 @@
       </c>
       <c r="B28" s="32">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A28)</f>
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
@@ -5670,7 +6141,7 @@
       </c>
       <c r="B30" s="32">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A30)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
@@ -5722,7 +6193,7 @@
       </c>
       <c r="B35" s="32">
         <f>COUNTIF('GUARDA MAT. ERRADO'!E3:E202,A35)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D35" s="18"/>
       <c r="E35" s="18"/>

--- a/Controle_Operacional_Final.xlsx
+++ b/Controle_Operacional_Final.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C782544C-EE9C-43F6-A5BA-25B834C234BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="1" r:id="rId1"/>
@@ -1602,6 +1602,40 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1624,40 +1658,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2407,7 +2407,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="44"/>
@@ -2429,7 +2429,7 @@
       <c r="R1" s="44"/>
     </row>
     <row r="2" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55"/>
+      <c r="A2" s="45"/>
       <c r="B2" s="44"/>
       <c r="C2" s="44"/>
       <c r="D2" s="44"/>
@@ -2449,7 +2449,7 @@
       <c r="R2" s="44"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="56" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="44"/>
@@ -2471,7 +2471,7 @@
       <c r="R3" s="44"/>
     </row>
     <row r="4" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="53" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="44"/>
@@ -2493,64 +2493,64 @@
       <c r="R4" s="44"/>
     </row>
     <row r="5" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="60" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="61" t="s">
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="62" t="s">
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="N5" s="53"/>
-      <c r="O5" s="53"/>
-      <c r="P5" s="53"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
     </row>
     <row r="6" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52">
+      <c r="A6" s="64">
         <f ca="1">SUMPRODUCT((MONTH('GUARDA MAT. ERRADO'!A3:A102)=MONTH(TODAY()))*(YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))+SUMPRODUCT((MONTH(CONFERENTES!A3:A102)=MONTH(TODAY()))*(YEAR(CONFERENTES!A3:A102)=YEAR(TODAY()))*(CONFERENTES!A3:A102&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="56">
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="46">
         <f ca="1">SUMPRODUCT((MONTH('GUARDA MAT. ERRADO'!A3:A102)=MONTH(TODAY()))*(YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="57">
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="48">
         <f ca="1">SUMPRODUCT((MONTH(CONFERENTES!A3:A102)=MONTH(TODAY()))*(YEAR(CONFERENTES!A3:A102)=YEAR(TODAY()))*(CONFERENTES!A3:A102&lt;&gt;""))</f>
         <v>0</v>
       </c>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="58">
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="49">
         <f ca="1">SUMPRODUCT((YEAR('GUARDA MAT. ERRADO'!A3:A102)=YEAR(TODAY()))*('GUARDA MAT. ERRADO'!A3:A102&lt;&gt;""))+SUMPRODUCT((YEAR(CONFERENTES!A3:A102)=YEAR(TODAY()))*(CONFERENTES!A3:A102&lt;&gt;""))</f>
         <v>83</v>
       </c>
-      <c r="N6" s="53"/>
-      <c r="O6" s="53"/>
-      <c r="P6" s="53"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
     </row>
     <row r="7" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="53" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="44"/>
@@ -2573,36 +2573,36 @@
     </row>
     <row r="27" spans="12:18" ht="71.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="12:18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L28" s="48" t="s">
+      <c r="L28" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
+      <c r="M28" s="60"/>
+      <c r="N28" s="60"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
     </row>
     <row r="29" spans="12:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M29" s="49" t="s">
+      <c r="M29" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="51"/>
+      <c r="N29" s="62"/>
+      <c r="O29" s="62"/>
+      <c r="P29" s="62"/>
+      <c r="Q29" s="62"/>
+      <c r="R29" s="63"/>
     </row>
     <row r="30" spans="12:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="L30" s="46" t="s">
+      <c r="L30" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
+      <c r="M30" s="59"/>
+      <c r="N30" s="59"/>
+      <c r="O30" s="59"/>
     </row>
     <row r="31" spans="12:18" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L31" s="34" t="s">
@@ -2761,12 +2761,12 @@
       </c>
     </row>
     <row r="43" spans="12:15" x14ac:dyDescent="0.25">
-      <c r="L43" s="45" t="s">
+      <c r="L43" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="M43" s="45"/>
-      <c r="N43" s="45"/>
-      <c r="O43" s="45"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="57"/>
     </row>
     <row r="44" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L44" s="35" t="s">
@@ -2933,6 +2933,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="L43:O43"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L28:R28"/>
+    <mergeCell ref="M29:R29"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A8:R8"/>
     <mergeCell ref="A2:R2"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:L6"/>
@@ -2944,12 +2950,6 @@
     <mergeCell ref="M5:P5"/>
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A3:R3"/>
-    <mergeCell ref="L43:O43"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L28:R28"/>
-    <mergeCell ref="M29:R29"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A8:R8"/>
   </mergeCells>
   <conditionalFormatting sqref="O31:R39 P30:R30">
     <cfRule type="top10" dxfId="0" priority="2" rank="1"/>
